--- a/public/downloads/HossainInvestigation2022.xlsx
+++ b/public/downloads/HossainInvestigation2022.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
@@ -659,10 +682,10 @@
         <v>735</v>
       </c>
       <c r="N3" s="5">
-        <v>3591.225170612335</v>
+        <v>3591225.170612335</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03351180137372353</v>
+        <v>33.51180137372353</v>
       </c>
       <c r="P3" s="5">
         <v>107163</v>
@@ -709,10 +732,10 @@
         <v>735</v>
       </c>
       <c r="N4" s="5">
-        <v>8140.631614208221</v>
+        <v>8140631.614208221</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05085479156280905</v>
+        <v>50.85479156280905</v>
       </c>
       <c r="P4" s="5">
         <v>160076</v>
@@ -759,10 +782,10 @@
         <v>735</v>
       </c>
       <c r="N5" s="5">
-        <v>12610.11402773857</v>
+        <v>12610114.02773857</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1320555238476775</v>
+        <v>132.0555238476775</v>
       </c>
       <c r="P5" s="5">
         <v>95491</v>
@@ -809,10 +832,10 @@
         <v>735</v>
       </c>
       <c r="N6" s="5">
-        <v>10533.07145786285</v>
+        <v>10533071.45786285</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08629845361776635</v>
+        <v>86.29845361776636</v>
       </c>
       <c r="P6" s="5">
         <v>122054</v>
@@ -859,10 +882,10 @@
         <v>735</v>
       </c>
       <c r="N7" s="5">
-        <v>16934.81539726257</v>
+        <v>16934815.39726257</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1993058103221478</v>
+        <v>199.3058103221477</v>
       </c>
       <c r="P7" s="5">
         <v>84969</v>
@@ -909,10 +932,10 @@
         <v>735</v>
       </c>
       <c r="N8" s="5">
-        <v>2446.888245105743</v>
+        <v>2446888.245105743</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01428814820824011</v>
+        <v>14.28814820824011</v>
       </c>
       <c r="P8" s="5">
         <v>171253</v>
@@ -959,10 +982,10 @@
         <v>735</v>
       </c>
       <c r="N9" s="5">
-        <v>2851.220616340637</v>
+        <v>2851220.616340637</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02783905774708193</v>
+        <v>27.83905774708193</v>
       </c>
       <c r="P9" s="5">
         <v>102418</v>
@@ -1009,10 +1032,10 @@
         <v>735</v>
       </c>
       <c r="N10" s="5">
-        <v>8098.537038803101</v>
+        <v>8098537.038803101</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08184804882262144</v>
+        <v>81.84804882262144</v>
       </c>
       <c r="P10" s="5">
         <v>98946</v>
@@ -1059,10 +1082,10 @@
         <v>735</v>
       </c>
       <c r="N11" s="5">
-        <v>3149.986998081207</v>
+        <v>3149986.998081207</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03845152034376054</v>
+        <v>38.45152034376054</v>
       </c>
       <c r="P11" s="5">
         <v>81921</v>
@@ -1109,10 +1132,10 @@
         <v>735</v>
       </c>
       <c r="N12" s="5">
-        <v>1509.623995542526</v>
+        <v>1509623.995542526</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01880167383478461</v>
+        <v>18.80167383478462</v>
       </c>
       <c r="P12" s="5">
         <v>80292</v>
@@ -1159,10 +1182,10 @@
         <v>735</v>
       </c>
       <c r="N13" s="5">
-        <v>12034.79246258736</v>
+        <v>12034792.46258736</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07458904022725635</v>
+        <v>74.58904022725635</v>
       </c>
       <c r="P13" s="5">
         <v>161348</v>
@@ -1209,10 +1232,10 @@
         <v>735</v>
       </c>
       <c r="N14" s="5">
-        <v>40650.07968759537</v>
+        <v>40650079.68759537</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2757844725681174</v>
+        <v>275.7844725681174</v>
       </c>
       <c r="P14" s="5">
         <v>147398</v>
@@ -1259,10 +1282,10 @@
         <v>735</v>
       </c>
       <c r="N15" s="5">
-        <v>18979.61919784546</v>
+        <v>18979619.19784546</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2704843905121273</v>
+        <v>270.4843905121273</v>
       </c>
       <c r="P15" s="5">
         <v>70169</v>
@@ -1309,10 +1332,10 @@
         <v>735</v>
       </c>
       <c r="N16" s="5">
-        <v>16806.18502116203</v>
+        <v>16806185.02116203</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09707711914812694</v>
+        <v>97.07711914812694</v>
       </c>
       <c r="P16" s="5">
         <v>173122</v>
@@ -1359,10 +1382,10 @@
         <v>735</v>
       </c>
       <c r="N17" s="5">
-        <v>7596.282861948013</v>
+        <v>7596282.861948013</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09790538307403224</v>
+        <v>97.90538307403224</v>
       </c>
       <c r="P17" s="5">
         <v>77588</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2585049132554452</v>
+        <v>0.2446266189895495</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2496739908439059</v>
+        <v>0.2254914604439605</v>
       </c>
       <c r="D3" s="4">
-        <v>0.214907741599165</v>
+        <v>0.2296485184906986</v>
       </c>
       <c r="E3" s="4">
-        <v>90.46435560525562</v>
+        <v>83.83934395676106</v>
       </c>
       <c r="F3" s="4">
-        <v>89.11685207318237</v>
+        <v>82.1818822592018</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="I3" s="5">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J3" s="5">
         <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.03978048551221355</v>
+      </c>
+      <c r="O3" s="5">
+        <v>317</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2481803437256181</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2266661915509577</v>
+      </c>
+      <c r="R3" s="5">
+        <v>316</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2812395780548758</v>
+        <v>0.3011335665457852</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2491388676402185</v>
+        <v>0.2625734103496017</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2372727888646287</v>
+        <v>0.2855976210844831</v>
       </c>
       <c r="E4" s="4">
-        <v>90.87932159165041</v>
+        <v>85.58102693132031</v>
       </c>
       <c r="F4" s="4">
-        <v>90.07995464435689</v>
+        <v>85.62946278079073</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J4" s="5">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.0253951113157014</v>
+      </c>
+      <c r="O4" s="5">
+        <v>319</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.304650687870776</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2669399680743547</v>
+      </c>
+      <c r="R4" s="5">
+        <v>318</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7322578329104701</v>
+        <v>0.6981181494256876</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1098881047384968</v>
+        <v>0.6827883525440086</v>
       </c>
       <c r="D5" s="4">
-        <v>0.467942171092659</v>
+        <v>0.5411392187988667</v>
       </c>
       <c r="E5" s="4">
-        <v>80.578231292517</v>
+        <v>78.16326530612245</v>
       </c>
       <c r="F5" s="4">
-        <v>69.50559284116332</v>
+        <v>68.75167785234899</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>3</v>
       </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
+      <c r="P5" s="4">
+        <v>0.6981181494256876</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6827883525440086</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1703,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1722,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1764,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1795,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2259497870855016</v>
+        <v>0.2728154089202643</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2220018526173163</v>
+        <v>0.2555741743365292</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2129671401140199</v>
+        <v>0.2470771298249724</v>
       </c>
       <c r="E3" s="4">
-        <v>87.94138477308734</v>
+        <v>82.99897493243846</v>
       </c>
       <c r="F3" s="4">
-        <v>89.16214642517848</v>
+        <v>84.51441880420354</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="I3" s="5">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.08966495212242775</v>
+      </c>
+      <c r="O3" s="5">
+        <v>328</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2712263144713668</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2541347250381398</v>
+      </c>
+      <c r="R3" s="5">
+        <v>328</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2710042791532905</v>
+        <v>0.3457339348890358</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2710042791532905</v>
+        <v>0.3455508939892891</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2708424902037673</v>
+        <v>0.3578963879863536</v>
       </c>
       <c r="E4" s="4">
-        <v>88.63367812878577</v>
+        <v>83.39325319168765</v>
       </c>
       <c r="F4" s="4">
-        <v>90.66881186601694</v>
+        <v>85.22236523551304</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2504527031451508</v>
+      </c>
+      <c r="O4" s="5">
+        <v>347</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2629500159834841</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2604196819180432</v>
+      </c>
+      <c r="R4" s="5">
+        <v>347</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8487777587075129</v>
+        <v>0.7391613981230535</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1667793011059189</v>
+        <v>0.7709719760644589</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6008162694463977</v>
+        <v>0.6505163303150653</v>
       </c>
       <c r="E5" s="4">
-        <v>78.93877551020408</v>
+        <v>78.00680272108842</v>
       </c>
       <c r="F5" s="4">
-        <v>67.22595078299777</v>
+        <v>68.11409395973149</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7391613981230535</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7709719760644589</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2001,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2020,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2062,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2093,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.246632560759089</v>
+        <v>0.2585049132554452</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2432163361918041</v>
+        <v>0.2496739908439059</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2220820933088341</v>
+        <v>0.214907741599165</v>
       </c>
       <c r="E3" s="4">
-        <v>92.08079396142027</v>
+        <v>90.46435560525562</v>
       </c>
       <c r="F3" s="4">
-        <v>91.02365848426494</v>
+        <v>89.11685207318237</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I3" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08881111340410121</v>
+      </c>
+      <c r="O3" s="5">
+        <v>340</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2392660760507461</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2277157533630842</v>
+      </c>
+      <c r="R3" s="5">
+        <v>339</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2372311724182167</v>
+        <v>0.2812395780548758</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2281509126794336</v>
+        <v>0.2491388676402185</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2138487687749959</v>
+        <v>0.2372727888646287</v>
       </c>
       <c r="E4" s="4">
-        <v>92.37824993010908</v>
+        <v>90.87932159165041</v>
       </c>
       <c r="F4" s="4">
-        <v>92.10811804725715</v>
+        <v>90.07995464435689</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.06375454915955404</v>
+      </c>
+      <c r="O4" s="5">
+        <v>344</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2625906986259608</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2318042978122983</v>
+      </c>
+      <c r="R4" s="5">
+        <v>344</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9306727286476985</v>
+        <v>0.7322578329104701</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2766822554211217</v>
+        <v>0.1098881047384968</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5148402783439792</v>
+        <v>0.467942171092659</v>
       </c>
       <c r="E5" s="4">
-        <v>83.54421768707482</v>
+        <v>80.578231292517</v>
       </c>
       <c r="F5" s="4">
-        <v>75.8255033557047</v>
+        <v>69.50559284116332</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>2</v>
       </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.7322578329104701</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1098881047384968</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2299,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2318,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2360,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,107 +2391,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2537385192089145</v>
+        <v>0.2259497870855016</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2253679661409483</v>
+        <v>0.2220018526173163</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2290071089631125</v>
+        <v>0.2129671401140199</v>
       </c>
       <c r="E3" s="4">
-        <v>81.56928524834581</v>
+        <v>87.94138477308734</v>
       </c>
       <c r="F3" s="4">
-        <v>78.92127118384343</v>
+        <v>89.16214642517848</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="I3" s="5">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.02029433468415415</v>
+      </c>
+      <c r="O3" s="5">
+        <v>357</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2275332681093336</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2233934303062857</v>
+      </c>
+      <c r="R3" s="5">
+        <v>357</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4265988617063718</v>
+        <v>0.2710042791532905</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3840245532846015</v>
+        <v>0.2710042791532905</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4756197930616574</v>
+        <v>0.2708424902037673</v>
       </c>
       <c r="E4" s="4">
-        <v>82.4261485416084</v>
+        <v>88.63367812878577</v>
       </c>
       <c r="F4" s="4">
-        <v>79.69970273666172</v>
+        <v>90.66881186601694</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>288</v>
+        <v>365</v>
       </c>
       <c r="I4" s="5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1722398184171729</v>
+      </c>
+      <c r="O4" s="5">
+        <v>365</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.237464696272652</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.237464696272652</v>
+      </c>
+      <c r="R4" s="5">
+        <v>365</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6416624917851663</v>
+        <v>0.8487777587075129</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2240259433398819</v>
+        <v>0.1667793011059189</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6611232391132831</v>
+        <v>0.6008162694463977</v>
       </c>
       <c r="E5" s="4">
-        <v>72.65986394557824</v>
+        <v>78.93877551020408</v>
       </c>
       <c r="F5" s="4">
-        <v>57.94183445190157</v>
+        <v>67.22595078299777</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -2208,23 +2554,39 @@
         <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8487777587075129</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1667793011059189</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2597,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2605,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2616,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2658,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2689,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5614660122356582</v>
+        <v>0.246632560759089</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5150547474543617</v>
+        <v>0.2432163361918041</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6697204505086179</v>
+        <v>0.2220820933088341</v>
       </c>
       <c r="E3" s="4">
-        <v>60.23679060665378</v>
+        <v>92.08079396142027</v>
       </c>
       <c r="F3" s="4">
-        <v>68.99080628849879</v>
+        <v>91.02365848426494</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="I3" s="5">
         <v>16</v>
       </c>
       <c r="J3" s="5">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0748982899564872</v>
+      </c>
+      <c r="O3" s="5">
+        <v>346</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2276963665718054</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2251208336837241</v>
+      </c>
+      <c r="R3" s="5">
+        <v>346</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.175668310989838</v>
+        <v>0.2372311724182167</v>
       </c>
       <c r="C4" s="4">
-        <v>1.150193618878783</v>
+        <v>0.2281509126794336</v>
       </c>
       <c r="D4" s="4">
-        <v>1.253844048567116</v>
+        <v>0.2138487687749959</v>
       </c>
       <c r="E4" s="4">
-        <v>60.13829093281134</v>
+        <v>92.37824993010908</v>
       </c>
       <c r="F4" s="4">
-        <v>69.11243909166147</v>
+        <v>92.10811804725715</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>154</v>
+        <v>355</v>
       </c>
       <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
         <v>7</v>
       </c>
-      <c r="J4" s="5">
-        <v>204</v>
-      </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>193</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.0303069367681279</v>
+      </c>
+      <c r="O4" s="5">
+        <v>355</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2333103889061696</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2242904278671493</v>
+      </c>
+      <c r="R4" s="5">
+        <v>355</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8678981396689821</v>
+        <v>0.9306727286476985</v>
       </c>
       <c r="C5" s="4">
-        <v>0.02981874516541438</v>
+        <v>0.2766822554211217</v>
       </c>
       <c r="D5" s="4">
-        <v>1.019295113914151</v>
+        <v>0.5148402783439792</v>
       </c>
       <c r="E5" s="4">
-        <v>36.22448979591837</v>
+        <v>83.54421768707482</v>
       </c>
       <c r="F5" s="4">
-        <v>44.14093959731544</v>
+        <v>75.8255033557047</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>3</v>
       </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
+      <c r="P5" s="4">
+        <v>0.9306727286476985</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2766822554211217</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2895,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2914,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2956,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2987,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4832519207930179</v>
+        <v>0.2537385192089145</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4781580739747834</v>
+        <v>0.2253679661409483</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4618877557320192</v>
+        <v>0.2290071089631125</v>
       </c>
       <c r="E3" s="4">
-        <v>93.56630323362219</v>
+        <v>81.56928524834581</v>
       </c>
       <c r="F3" s="4">
-        <v>92.52526738377649</v>
+        <v>78.92127118384343</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>352</v>
+        <v>306</v>
       </c>
       <c r="I3" s="5">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.005260105668488329</v>
+      </c>
+      <c r="O3" s="5">
+        <v>307</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2528162513221546</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2248007618829606</v>
+      </c>
+      <c r="R3" s="5">
+        <v>306</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3967705815512829</v>
+        <v>0.4265988617063718</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3962362821978118</v>
+        <v>0.3840245532846015</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3763345136464105</v>
+        <v>0.4756197930616574</v>
       </c>
       <c r="E4" s="4">
-        <v>94.43276488677664</v>
+        <v>82.4261485416084</v>
       </c>
       <c r="F4" s="4">
-        <v>94.16790781771907</v>
+        <v>79.69970273666172</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.361823703081217</v>
+      </c>
+      <c r="O4" s="5">
+        <v>289</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3297225949591256</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2258962597197854</v>
+      </c>
+      <c r="R4" s="5">
+        <v>289</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.383716821302767</v>
+        <v>0.6416624917851663</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6441604323722885</v>
+        <v>0.2240259433398819</v>
       </c>
       <c r="D5" s="4">
-        <v>0.8439222689765871</v>
+        <v>0.6611232391132831</v>
       </c>
       <c r="E5" s="4">
-        <v>85.06802721088431</v>
+        <v>72.65986394557824</v>
       </c>
       <c r="F5" s="4">
-        <v>77.79194630872483</v>
+        <v>57.94183445190157</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6416624917851663</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2240259433398819</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3193,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3212,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3254,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,116 +3285,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4799770281230815</v>
+        <v>0.5614660122356582</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4535202705273959</v>
+        <v>0.5150547474543617</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5973545367062015</v>
+        <v>0.6697204505086179</v>
       </c>
       <c r="E3" s="4">
-        <v>61.04482340881584</v>
+        <v>60.23679060665378</v>
       </c>
       <c r="F3" s="4">
-        <v>67.984186816217</v>
+        <v>68.99080628849879</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="I3" s="5">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="J3" s="5">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4350313666044115</v>
+      </c>
+      <c r="O3" s="5">
+        <v>219</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3061439470017244</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2783959606552073</v>
+      </c>
+      <c r="R3" s="5">
+        <v>218</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.319664506082364</v>
+        <v>1.175668310989838</v>
       </c>
       <c r="C4" s="4">
-        <v>1.361753772558982</v>
+        <v>1.150193618878783</v>
       </c>
       <c r="D4" s="4">
-        <v>1.335756116324884</v>
+        <v>1.253844048567116</v>
       </c>
       <c r="E4" s="4">
-        <v>59.35374149659864</v>
+        <v>60.13829093281134</v>
       </c>
       <c r="F4" s="4">
-        <v>67.62550948484535</v>
+        <v>69.11243909166147</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="I4" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="M4" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>11</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.217265215074589</v>
+      </c>
+      <c r="O4" s="5">
+        <v>165</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5448416150750371</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5018673484932957</v>
+      </c>
+      <c r="R4" s="5">
+        <v>165</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8794234845177172</v>
+        <v>0.8678981396689821</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.02981874516541438</v>
       </c>
       <c r="D5" s="4">
-        <v>1.036538675741868</v>
+        <v>1.019295113914151</v>
       </c>
       <c r="E5" s="4">
-        <v>35.24489795918367</v>
+        <v>36.22448979591837</v>
       </c>
       <c r="F5" s="4">
-        <v>37.19015659955276</v>
+        <v>44.14093959731544</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -2861,9 +3462,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8678981396689821</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.02981874516541438</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3491,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3499,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3510,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3552,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,81 +3583,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3498424429858797</v>
+        <v>0.4832519207930179</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3443645504649553</v>
+        <v>0.4781580739747834</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3133497679057756</v>
+        <v>0.4618877557320192</v>
       </c>
       <c r="E3" s="4">
-        <v>92.06588388780175</v>
+        <v>93.56630323362219</v>
       </c>
       <c r="F3" s="4">
-        <v>89.66982317428173</v>
+        <v>92.52526738377649</v>
       </c>
       <c r="G3" s="5">
         <v>365</v>
       </c>
       <c r="H3" s="5">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="I3" s="5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4156153111819387</v>
+      </c>
+      <c r="O3" s="5">
+        <v>352</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2204971697653928</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2180163710188783</v>
+      </c>
+      <c r="R3" s="5">
+        <v>352</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3226005715993019</v>
+        <v>0.3967705815512829</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3171986508296905</v>
+        <v>0.3962362821978118</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2880511340440732</v>
+        <v>0.3763345136464105</v>
       </c>
       <c r="E4" s="4">
-        <v>93.74596962072492</v>
+        <v>94.43276488677664</v>
       </c>
       <c r="F4" s="4">
-        <v>93.42048971836702</v>
+        <v>94.16790781771907</v>
       </c>
       <c r="G4" s="5">
         <v>365</v>
       </c>
       <c r="H4" s="5">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I4" s="5">
         <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -3033,50 +3701,84 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3114844461529672</v>
+      </c>
+      <c r="O4" s="5">
+        <v>363</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2393151938665863</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2396295394633538</v>
+      </c>
+      <c r="R4" s="5">
+        <v>363</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8343189176219766</v>
+        <v>1.383716821302767</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2726947277784054</v>
+        <v>0.6441604323722885</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5718089219231957</v>
+        <v>0.8439222689765871</v>
       </c>
       <c r="E5" s="4">
-        <v>87.22448979591837</v>
+        <v>85.06802721088431</v>
       </c>
       <c r="F5" s="4">
-        <v>77.57046979865773</v>
+        <v>77.79194630872483</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
         <v>3</v>
       </c>
-      <c r="I5" s="5">
+      <c r="P5" s="4">
+        <v>1.383716821302767</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6441604323722885</v>
+      </c>
+      <c r="R5" s="5">
         <v>2</v>
       </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3789,1462 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4799770281230815</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4535202705273959</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5973545367062015</v>
+      </c>
+      <c r="E3" s="4">
+        <v>61.04482340881584</v>
+      </c>
+      <c r="F3" s="4">
+        <v>67.984186816217</v>
+      </c>
+      <c r="G3" s="5">
+        <v>365</v>
+      </c>
+      <c r="H3" s="5">
+        <v>204</v>
+      </c>
+      <c r="I3" s="5">
+        <v>76</v>
+      </c>
+      <c r="J3" s="5">
+        <v>85</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>85</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3642792200152736</v>
+      </c>
+      <c r="O3" s="5">
+        <v>204</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2923282263749287</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2683072031370115</v>
+      </c>
+      <c r="R3" s="5">
+        <v>203</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.319664506082364</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.361753772558982</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.335756116324884</v>
+      </c>
+      <c r="E4" s="4">
+        <v>59.35374149659864</v>
+      </c>
+      <c r="F4" s="4">
+        <v>67.62550948484535</v>
+      </c>
+      <c r="G4" s="5">
+        <v>365</v>
+      </c>
+      <c r="H4" s="5">
+        <v>128</v>
+      </c>
+      <c r="I4" s="5">
+        <v>9</v>
+      </c>
+      <c r="J4" s="5">
+        <v>228</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>216</v>
+      </c>
+      <c r="M4" s="5">
+        <v>12</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.42847519041751</v>
+      </c>
+      <c r="O4" s="5">
+        <v>140</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.50131293113547</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3587353769935242</v>
+      </c>
+      <c r="R4" s="5">
+        <v>140</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.8794234845177172</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>1.036538675741868</v>
+      </c>
+      <c r="E5" s="4">
+        <v>35.24489795918367</v>
+      </c>
+      <c r="F5" s="4">
+        <v>37.19015659955276</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8794234845177172</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3498424429858797</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3443645504649553</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3133497679057756</v>
+      </c>
+      <c r="E3" s="4">
+        <v>92.06588388780175</v>
+      </c>
+      <c r="F3" s="4">
+        <v>89.66982317428173</v>
+      </c>
+      <c r="G3" s="5">
+        <v>365</v>
+      </c>
+      <c r="H3" s="5">
+        <v>341</v>
+      </c>
+      <c r="I3" s="5">
+        <v>19</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2464482651060732</v>
+      </c>
+      <c r="O3" s="5">
+        <v>341</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2248679064568086</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2124036193552077</v>
+      </c>
+      <c r="R3" s="5">
+        <v>340</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3226005715993019</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3171986508296905</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2880511340440732</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.74596962072492</v>
+      </c>
+      <c r="F4" s="4">
+        <v>93.42048971836702</v>
+      </c>
+      <c r="G4" s="5">
+        <v>365</v>
+      </c>
+      <c r="H4" s="5">
+        <v>362</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.221291629975281</v>
+      </c>
+      <c r="O4" s="5">
+        <v>362</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2215167140400358</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2158883845889257</v>
+      </c>
+      <c r="R4" s="5">
+        <v>362</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.8343189176219766</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2726947277784054</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5718089219231957</v>
+      </c>
+      <c r="E5" s="4">
+        <v>87.22448979591837</v>
+      </c>
+      <c r="F5" s="4">
+        <v>77.57046979865773</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8343189176219766</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2726947277784054</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>78.77551020408163</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13.06122448979592</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.163265306122449</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.9523809523809524</v>
+      </c>
+      <c r="F3" s="3">
+        <v>7.210884353741497</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2686848266364926</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2326727226172738</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2639634392419071</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.78726456569022</v>
+      </c>
+      <c r="L3" s="4">
+        <v>84.24103243086942</v>
+      </c>
+      <c r="M3" s="5">
+        <v>735</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3591225.170612335</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.51180137372353</v>
+      </c>
+      <c r="P3" s="5">
+        <v>107163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>83.80952380952381</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.843537414965986</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.346938775510205</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.537414965986395</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3.401360544217687</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.320729233539302</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2438151552655745</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.255560286267519</v>
+      </c>
+      <c r="K4" s="4">
+        <v>87.04229719098485</v>
+      </c>
+      <c r="L4" s="4">
+        <v>85.05306731193561</v>
+      </c>
+      <c r="M4" s="5">
+        <v>735</v>
+      </c>
+      <c r="N4" s="5">
+        <v>8140631.614208221</v>
+      </c>
+      <c r="O4" s="4">
+        <v>50.85479156280905</v>
+      </c>
+      <c r="P4" s="5">
+        <v>160076</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="C5" s="3">
+        <v>6.258503401360545</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.312925170068027</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.768707482993197</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2645757626485283</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.249265271781267</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2405579543176286</v>
+      </c>
+      <c r="K5" s="4">
+        <v>87.47156277476991</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.07400812674106</v>
+      </c>
+      <c r="M5" s="5">
+        <v>735</v>
+      </c>
+      <c r="N5" s="5">
+        <v>12610114.02773857</v>
+      </c>
+      <c r="O5" s="4">
+        <v>132.0555238476775</v>
+      </c>
+      <c r="P5" s="5">
+        <v>95491</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>86.39455782312925</v>
+      </c>
+      <c r="C6" s="3">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.129251700680272</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.224489795918367</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1.63265306122449</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2660674284381063</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2179059389279547</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2248064485727185</v>
+      </c>
+      <c r="K6" s="4">
+        <v>87.04609190615018</v>
+      </c>
+      <c r="L6" s="4">
+        <v>85.68705961131654</v>
+      </c>
+      <c r="M6" s="5">
+        <v>735</v>
+      </c>
+      <c r="N6" s="5">
+        <v>10533071.45786285</v>
+      </c>
+      <c r="O6" s="4">
+        <v>86.29845361776636</v>
+      </c>
+      <c r="P6" s="5">
+        <v>122054</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>92.92517006802721</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5.578231292517007</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.496598639455782</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.08843537414966</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2383869076608513</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2234749080942682</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2097857673057082</v>
+      </c>
+      <c r="K7" s="4">
+        <v>89.5935027072054</v>
+      </c>
+      <c r="L7" s="4">
+        <v>89.35909844922458</v>
+      </c>
+      <c r="M7" s="5">
+        <v>735</v>
+      </c>
+      <c r="N7" s="5">
+        <v>16934815.39726257</v>
+      </c>
+      <c r="O7" s="4">
+        <v>199.3058103221477</v>
+      </c>
+      <c r="P7" s="5">
+        <v>84969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7.755102040816326</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5.578231292517007</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.489795918367347</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2792842411970235</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2489196097886648</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2551521270434528</v>
+      </c>
+      <c r="K8" s="4">
+        <v>84.66564857235382</v>
+      </c>
+      <c r="L8" s="4">
+        <v>83.80258412089664</v>
+      </c>
+      <c r="M8" s="5">
+        <v>735</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2446888.245105743</v>
+      </c>
+      <c r="O8" s="4">
+        <v>14.28814820824011</v>
+      </c>
+      <c r="P8" s="5">
+        <v>171253</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>92.24489795918367</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5.306122448979592</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.448979591836735</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2.176870748299319</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.2702995477641304</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2596382527526021</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2438293548410006</v>
+      </c>
+      <c r="K9" s="4">
+        <v>83.16081262436943</v>
+      </c>
+      <c r="L9" s="4">
+        <v>84.75441720312288</v>
+      </c>
+      <c r="M9" s="5">
+        <v>735</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2851220.616340637</v>
+      </c>
+      <c r="O9" s="4">
+        <v>27.83905774708193</v>
+      </c>
+      <c r="P9" s="5">
+        <v>102418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>93.06122448979592</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.80952380952381</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.129251700680272</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.224489795918367</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.63265306122449</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2542027373082318</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2295997177518343</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2177801792272032</v>
+      </c>
+      <c r="K10" s="4">
+        <v>90.60317460317447</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.46171757293543</v>
+      </c>
+      <c r="M10" s="5">
+        <v>735</v>
+      </c>
+      <c r="N10" s="5">
+        <v>8098537.038803101</v>
+      </c>
+      <c r="O10" s="4">
+        <v>81.84804882262144</v>
+      </c>
+      <c r="P10" s="5">
+        <v>98946</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>98.36734693877551</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.360544217687075</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2366913548203569</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2304188769847412</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2197788111256071</v>
+      </c>
+      <c r="K11" s="4">
+        <v>88.22393447174807</v>
+      </c>
+      <c r="L11" s="4">
+        <v>89.76112861251599</v>
+      </c>
+      <c r="M11" s="5">
+        <v>735</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3149986.998081207</v>
+      </c>
+      <c r="O11" s="4">
+        <v>38.45152034376054</v>
+      </c>
+      <c r="P11" s="5">
+        <v>81921</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>95.64625850340136</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.72108843537415</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.63265306122449</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.08843537414966</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2352664345478903</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2248481861426014</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2115410133671945</v>
+      </c>
+      <c r="K12" s="4">
+        <v>92.17043824332447</v>
+      </c>
+      <c r="L12" s="4">
+        <v>91.45881081739275</v>
+      </c>
+      <c r="M12" s="5">
+        <v>735</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1509623.995542526</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.80167383478462</v>
+      </c>
+      <c r="P12" s="5">
+        <v>80292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>81.08843537414965</v>
+      </c>
+      <c r="C13" s="3">
+        <v>13.60544217687075</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5.306122448979592</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.224489795918367</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.945578231292517</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2936530494579498</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.225330668017691</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2393055629591692</v>
+      </c>
+      <c r="K13" s="4">
+        <v>81.93419408579759</v>
+      </c>
+      <c r="L13" s="4">
+        <v>79.16512197720292</v>
+      </c>
+      <c r="M13" s="5">
+        <v>735</v>
+      </c>
+      <c r="N13" s="5">
+        <v>12034792.46258736</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.58904022725635</v>
+      </c>
+      <c r="P13" s="5">
+        <v>161348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>52.24489795918367</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.26530612244898</v>
+      </c>
+      <c r="D14" s="3">
+        <v>44.48979591836735</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>44.35374149659864</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.4285023413011739</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3737714861182145</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5695820146202505</v>
+      </c>
+      <c r="K14" s="4">
+        <v>60.02452681752987</v>
+      </c>
+      <c r="L14" s="4">
+        <v>68.88216226087734</v>
+      </c>
+      <c r="M14" s="5">
+        <v>735</v>
+      </c>
+      <c r="N14" s="5">
+        <v>40650079.68759537</v>
+      </c>
+      <c r="O14" s="4">
+        <v>275.7844725681174</v>
+      </c>
+      <c r="P14" s="5">
+        <v>147398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>97.55102040816327</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.5442176870748299</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.2721088435374149</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2377552337852874</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2301472891054214</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2137792852870748</v>
+      </c>
+      <c r="K15" s="4">
+        <v>93.93877551020434</v>
+      </c>
+      <c r="L15" s="4">
+        <v>93.24077371440788</v>
+      </c>
+      <c r="M15" s="5">
+        <v>735</v>
+      </c>
+      <c r="N15" s="5">
+        <v>18979619.19784546</v>
+      </c>
+      <c r="O15" s="4">
+        <v>270.4843905121273</v>
+      </c>
+      <c r="P15" s="5">
+        <v>70169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="C16" s="3">
+        <v>11.83673469387755</v>
+      </c>
+      <c r="D16" s="3">
+        <v>41.49659863945578</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>41.36054421768707</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4001035917195703</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.3052166618539555</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.566634879539166</v>
+      </c>
+      <c r="K16" s="4">
+        <v>60.02952473506402</v>
+      </c>
+      <c r="L16" s="4">
+        <v>67.59658494270185</v>
+      </c>
+      <c r="M16" s="5">
+        <v>735</v>
+      </c>
+      <c r="N16" s="5">
+        <v>16806185.02116203</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.07711914812694</v>
+      </c>
+      <c r="P16" s="5">
+        <v>173122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>95.91836734693877</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.129251700680272</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.9523809523809524</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.4081632653061225</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.1360544217687075</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2273496341081062</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2144495177096411</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2080672361182632</v>
+      </c>
+      <c r="K17" s="4">
+        <v>92.86727752325409</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.45009055076157</v>
+      </c>
+      <c r="M17" s="5">
+        <v>735</v>
+      </c>
+      <c r="N17" s="5">
+        <v>7596282.861948013</v>
+      </c>
+      <c r="O17" s="4">
+        <v>97.90538307403224</v>
+      </c>
+      <c r="P17" s="5">
+        <v>77588</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -3250,10 +5402,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L4" s="5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
@@ -3294,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
         <v>10</v>
@@ -3338,10 +5490,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L6" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -3382,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -3426,10 +5578,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L8" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -3470,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
         <v>16</v>
@@ -3514,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L10" s="5">
         <v>7</v>
@@ -3602,10 +5754,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L12" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -3646,10 +5798,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L13" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
@@ -3734,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="5">
         <v>1</v>
@@ -3822,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17" s="5">
         <v>0</v>
@@ -3847,9 +5999,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>579</v>
+      </c>
+      <c r="C3" s="5">
+        <v>96</v>
+      </c>
+      <c r="D3" s="5">
+        <v>60</v>
+      </c>
+      <c r="E3" s="5">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5">
+        <v>53</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>53</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>616</v>
+      </c>
+      <c r="C4" s="5">
+        <v>65</v>
+      </c>
+      <c r="D4" s="5">
+        <v>54</v>
+      </c>
+      <c r="E4" s="5">
+        <v>26</v>
+      </c>
+      <c r="F4" s="5">
+        <v>25</v>
+      </c>
+      <c r="G4" s="5">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>26</v>
+      </c>
+      <c r="I4" s="5">
+        <v>26</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>6</v>
+      </c>
+      <c r="L4" s="5">
+        <v>19</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>672</v>
+      </c>
+      <c r="C5" s="5">
+        <v>46</v>
+      </c>
+      <c r="D5" s="5">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>10</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>635</v>
+      </c>
+      <c r="C6" s="5">
+        <v>77</v>
+      </c>
+      <c r="D6" s="5">
+        <v>23</v>
+      </c>
+      <c r="E6" s="5">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5">
+        <v>9</v>
+      </c>
+      <c r="I6" s="5">
+        <v>9</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>6</v>
+      </c>
+      <c r="L6" s="5">
+        <v>6</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>683</v>
+      </c>
+      <c r="C7" s="5">
+        <v>41</v>
+      </c>
+      <c r="D7" s="5">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>5</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>637</v>
+      </c>
+      <c r="C8" s="5">
+        <v>57</v>
+      </c>
+      <c r="D8" s="5">
+        <v>41</v>
+      </c>
+      <c r="E8" s="5">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5">
+        <v>33</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
+        <v>6</v>
+      </c>
+      <c r="I8" s="5">
+        <v>6</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>18</v>
+      </c>
+      <c r="L8" s="5">
+        <v>16</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>678</v>
+      </c>
+      <c r="C9" s="5">
+        <v>39</v>
+      </c>
+      <c r="D9" s="5">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5">
+        <v>16</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>16</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>684</v>
+      </c>
+      <c r="C10" s="5">
+        <v>28</v>
+      </c>
+      <c r="D10" s="5">
+        <v>23</v>
+      </c>
+      <c r="E10" s="5">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5">
+        <v>9</v>
+      </c>
+      <c r="I10" s="5">
+        <v>9</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>3</v>
+      </c>
+      <c r="L10" s="5">
+        <v>7</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>723</v>
+      </c>
+      <c r="C11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>703</v>
+      </c>
+      <c r="C12" s="5">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3</v>
+      </c>
+      <c r="F12" s="5">
+        <v>8</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3</v>
+      </c>
+      <c r="I12" s="5">
+        <v>3</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>2</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>596</v>
+      </c>
+      <c r="C13" s="5">
+        <v>100</v>
+      </c>
+      <c r="D13" s="5">
+        <v>39</v>
+      </c>
+      <c r="E13" s="5">
+        <v>9</v>
+      </c>
+      <c r="F13" s="5">
+        <v>29</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
+        <v>9</v>
+      </c>
+      <c r="I13" s="5">
+        <v>9</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>12</v>
+      </c>
+      <c r="L13" s="5">
+        <v>17</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>384</v>
+      </c>
+      <c r="C14" s="5">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>327</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>326</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>211</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>717</v>
+      </c>
+      <c r="C15" s="5">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>343</v>
+      </c>
+      <c r="C16" s="5">
+        <v>87</v>
+      </c>
+      <c r="D16" s="5">
+        <v>305</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>304</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>239</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>705</v>
+      </c>
+      <c r="C17" s="5">
+        <v>23</v>
+      </c>
+      <c r="D17" s="5">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5">
+        <v>3</v>
+      </c>
+      <c r="F17" s="5">
+        <v>3</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>3</v>
+      </c>
+      <c r="I17" s="5">
+        <v>3</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>3</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6767,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6809,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6840,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2707772872519045</v>
@@ -3960,10 +6899,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.05210567036339144</v>
+      </c>
+      <c r="O3" s="5">
+        <v>320</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2588356415117281</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2422545293767273</v>
+      </c>
+      <c r="R3" s="5">
+        <v>320</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2924661441249538</v>
@@ -4001,10 +6958,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1673042143200807</v>
+      </c>
+      <c r="O4" s="5">
+        <v>257</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2729317752177752</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2146751242765272</v>
+      </c>
+      <c r="R4" s="5">
+        <v>257</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6776480943106776</v>
@@ -4042,9 +7017,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6776480943106776</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.012275027890638</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7046,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7065,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7107,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7138,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2713503463239055</v>
@@ -4173,10 +7197,28 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1161720967145131</v>
+      </c>
+      <c r="O3" s="5">
+        <v>361</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2587521640772868</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2519203203302235</v>
+      </c>
+      <c r="R3" s="5">
+        <v>360</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4643698666644595</v>
@@ -4214,10 +7256,28 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4428475574635733</v>
+      </c>
+      <c r="O4" s="5">
+        <v>255</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3598072784024535</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2313680700883081</v>
+      </c>
+      <c r="R4" s="5">
+        <v>255</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.992358029256354</v>
@@ -4255,9 +7315,25 @@
       <c r="M5" s="5">
         <v>2</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.992358029256354</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4999624521948363</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7344,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7363,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7405,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7436,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2674420343347005</v>
@@ -4386,10 +7495,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.02677545433932009</v>
+      </c>
+      <c r="O3" s="5">
+        <v>319</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2616401339763661</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2426203566410948</v>
+      </c>
+      <c r="R3" s="5">
+        <v>318</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2622401230849897</v>
@@ -4427,10 +7554,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.06156456835721322</v>
+      </c>
+      <c r="O4" s="5">
+        <v>352</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2623502581986522</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2562361345936407</v>
+      </c>
+      <c r="R4" s="5">
+        <v>352</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6413384805573173</v>
@@ -4468,9 +7613,25 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6413384805573173</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07893492409084502</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7642,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7661,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7703,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7734,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2596866171608976</v>
@@ -4599,10 +7793,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.06140516992203723</v>
+      </c>
+      <c r="O3" s="5">
+        <v>322</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.242864670178938</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2198412721208129</v>
+      </c>
+      <c r="R3" s="5">
+        <v>321</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2923050131111867</v>
@@ -4640,10 +7852,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1101429476718305</v>
+      </c>
+      <c r="O4" s="5">
+        <v>312</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2856580233802246</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2170246003519183</v>
+      </c>
+      <c r="R4" s="5">
+        <v>312</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5297553505827522</v>
@@ -4681,9 +7911,25 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5297553505827522</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04477377933591242</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7940,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7959,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8001,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8032,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2501201087726795</v>
@@ -4812,10 +8091,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0921354781380585</v>
+      </c>
+      <c r="O3" s="5">
+        <v>328</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2236029128414728</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2183766830978613</v>
+      </c>
+      <c r="R3" s="5">
+        <v>328</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2521450521932875</v>
@@ -4853,10 +8150,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03286159159880963</v>
+      </c>
+      <c r="O4" s="5">
+        <v>353</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2450928225115931</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2290472718525063</v>
+      </c>
+      <c r="R4" s="5">
+        <v>353</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.8280867453713313</v>
@@ -4894,9 +8209,25 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8280867453713313</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07606160417600449</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8238,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2446266189895495</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2254914604439605</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2296485184906986</v>
-      </c>
-      <c r="E3" s="4">
-        <v>83.83934395676106</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.1818822592018</v>
-      </c>
-      <c r="G3" s="5">
-        <v>365</v>
-      </c>
-      <c r="H3" s="5">
-        <v>316</v>
-      </c>
-      <c r="I3" s="5">
-        <v>43</v>
-      </c>
-      <c r="J3" s="5">
-        <v>6</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3011335665457852</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2625734103496017</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2855976210844831</v>
-      </c>
-      <c r="E4" s="4">
-        <v>85.58102693132031</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.62946278079073</v>
-      </c>
-      <c r="G4" s="5">
-        <v>365</v>
-      </c>
-      <c r="H4" s="5">
-        <v>318</v>
-      </c>
-      <c r="I4" s="5">
-        <v>13</v>
-      </c>
-      <c r="J4" s="5">
-        <v>34</v>
-      </c>
-      <c r="K4" s="5">
-        <v>5</v>
-      </c>
-      <c r="L4" s="5">
-        <v>28</v>
-      </c>
-      <c r="M4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6981181494256876</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6827883525440086</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5411392187988667</v>
-      </c>
-      <c r="E5" s="4">
-        <v>78.16326530612245</v>
-      </c>
-      <c r="F5" s="4">
-        <v>68.75167785234899</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2728154089202643</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2555741743365292</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2470771298249724</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.99897493243846</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.51441880420354</v>
-      </c>
-      <c r="G3" s="5">
-        <v>365</v>
-      </c>
-      <c r="H3" s="5">
-        <v>327</v>
-      </c>
-      <c r="I3" s="5">
-        <v>33</v>
-      </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3457339348890358</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3455508939892891</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3578963879863536</v>
-      </c>
-      <c r="E4" s="4">
-        <v>83.39325319168765</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.22236523551304</v>
-      </c>
-      <c r="G4" s="5">
-        <v>365</v>
-      </c>
-      <c r="H4" s="5">
-        <v>347</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>14</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>12</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7391613981230535</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7709719760644589</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6505163303150653</v>
-      </c>
-      <c r="E5" s="4">
-        <v>78.00680272108842</v>
-      </c>
-      <c r="F5" s="4">
-        <v>68.11409395973149</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/HossainInvestigation2022.xlsx
+++ b/public/downloads/HossainInvestigation2022.xlsx
@@ -1557,16 +1557,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03978048551221355</v>
+        <v>0.007267169147678221</v>
       </c>
       <c r="O3" s="5">
         <v>317</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2481803437256181</v>
+        <v>0.2448922208071104</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2266661915509577</v>
+        <v>0.2253612973097955</v>
       </c>
       <c r="R3" s="5">
         <v>316</v>
@@ -1616,16 +1616,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0253951113157014</v>
+        <v>-0.04681871043408048</v>
       </c>
       <c r="O4" s="5">
         <v>319</v>
       </c>
       <c r="P4" s="4">
-        <v>0.304650687870776</v>
+        <v>0.2984558254503137</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2669399680743547</v>
+        <v>0.2587637592426285</v>
       </c>
       <c r="R4" s="5">
         <v>318</v>
@@ -1855,16 +1855,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08966495212242775</v>
+        <v>0.07087810816651086</v>
       </c>
       <c r="O3" s="5">
         <v>328</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2712263144713668</v>
+        <v>0.2698086486653997</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2541347250381398</v>
+        <v>0.2537436241547965</v>
       </c>
       <c r="R3" s="5">
         <v>328</v>
@@ -1914,16 +1914,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2504527031451508</v>
+        <v>0.2600127657104565</v>
       </c>
       <c r="O4" s="5">
         <v>347</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2629500159834841</v>
+        <v>0.2629504380524407</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2604196819180432</v>
+        <v>0.2603099234307462</v>
       </c>
       <c r="R4" s="5">
         <v>347</v>
@@ -2153,16 +2153,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08881111340410121</v>
+        <v>-0.09399076335182488</v>
       </c>
       <c r="O3" s="5">
         <v>340</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2392660760507461</v>
+        <v>0.2390309852101484</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2277157533630842</v>
+        <v>0.2276459823971684</v>
       </c>
       <c r="R3" s="5">
         <v>339</v>
@@ -2212,16 +2212,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06375454915955404</v>
+        <v>-0.1152958237520934</v>
       </c>
       <c r="O4" s="5">
         <v>344</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2625906986259608</v>
+        <v>0.2562913734706496</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2318042978122983</v>
+        <v>0.2265312074131606</v>
       </c>
       <c r="R4" s="5">
         <v>344</v>
@@ -2451,16 +2451,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02029433468415415</v>
+        <v>-0.008975346989728905</v>
       </c>
       <c r="O3" s="5">
         <v>357</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2275332681093336</v>
+        <v>0.225721968955372</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2233934303062857</v>
+        <v>0.2218694934309343</v>
       </c>
       <c r="R3" s="5">
         <v>357</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1722398184171729</v>
+        <v>0.1494312339306418</v>
       </c>
       <c r="O4" s="5">
         <v>365</v>
       </c>
       <c r="P4" s="4">
-        <v>0.237464696272652</v>
+        <v>0.2367115311909247</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.237464696272652</v>
+        <v>0.2367115311909247</v>
       </c>
       <c r="R4" s="5">
         <v>365</v>
@@ -2749,22 +2749,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0748982899564872</v>
+        <v>-0.1063381206921292</v>
       </c>
       <c r="O3" s="5">
         <v>346</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2276963665718054</v>
+        <v>0.2257313916161702</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2251208336837241</v>
+        <v>0.2181026678796981</v>
       </c>
       <c r="R3" s="5">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2808,16 +2808,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.0303069367681279</v>
+        <v>-0.05081944533446858</v>
       </c>
       <c r="O4" s="5">
         <v>355</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2333103889061696</v>
+        <v>0.2322263757336254</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2242904278671493</v>
+        <v>0.2232914425408227</v>
       </c>
       <c r="R4" s="5">
         <v>355</v>
@@ -3047,16 +3047,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.005260105668488329</v>
+        <v>-0.02926631709470939</v>
       </c>
       <c r="O3" s="5">
         <v>307</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2528162513221546</v>
+        <v>0.249767940994007</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2248007618829606</v>
+        <v>0.2235038970281861</v>
       </c>
       <c r="R3" s="5">
         <v>306</v>
@@ -3106,16 +3106,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.361823703081217</v>
+        <v>0.3365944735205062</v>
       </c>
       <c r="O4" s="5">
         <v>289</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3297225949591256</v>
+        <v>0.3255687770692435</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2258962597197854</v>
+        <v>0.2247803568779743</v>
       </c>
       <c r="R4" s="5">
         <v>289</v>
@@ -3345,16 +3345,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4350313666044115</v>
+        <v>-0.487228379550618</v>
       </c>
       <c r="O3" s="5">
         <v>219</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3061439470017244</v>
+        <v>0.2978990426907761</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2783959606552073</v>
+        <v>0.2744229795048873</v>
       </c>
       <c r="R3" s="5">
         <v>218</v>
@@ -3404,16 +3404,16 @@
         <v>11</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.217265215074589</v>
+        <v>-1.303144887816358</v>
       </c>
       <c r="O4" s="5">
         <v>165</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5448416150750371</v>
+        <v>0.5500698780112966</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5018673484932957</v>
+        <v>0.4987251968998097</v>
       </c>
       <c r="R4" s="5">
         <v>165</v>
@@ -3643,22 +3643,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4156153111819387</v>
+        <v>-0.4512741123239206</v>
       </c>
       <c r="O3" s="5">
         <v>352</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2204971697653928</v>
+        <v>0.2168180232773852</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2180163710188783</v>
+        <v>0.2096166348397868</v>
       </c>
       <c r="R3" s="5">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3702,16 +3702,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3114844461529672</v>
+        <v>-0.3374182068783504</v>
       </c>
       <c r="O4" s="5">
         <v>363</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2393151938665863</v>
+        <v>0.2383391851577615</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2396295394633538</v>
+        <v>0.2387910390301022</v>
       </c>
       <c r="R4" s="5">
         <v>363</v>
@@ -3941,16 +3941,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3642792200152736</v>
+        <v>-0.4000434532064305</v>
       </c>
       <c r="O3" s="5">
         <v>204</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2923282263749287</v>
+        <v>0.2887779614454291</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2683072031370115</v>
+        <v>0.2665908098944525</v>
       </c>
       <c r="R3" s="5">
         <v>203</v>
@@ -4000,16 +4000,16 @@
         <v>12</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.42847519041751</v>
+        <v>-1.47053497682967</v>
       </c>
       <c r="O4" s="5">
         <v>140</v>
       </c>
       <c r="P4" s="4">
-        <v>0.50131293113547</v>
+        <v>0.5080342259730323</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3587353769935242</v>
+        <v>0.3567873461169113</v>
       </c>
       <c r="R4" s="5">
         <v>140</v>
@@ -4235,16 +4235,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2464482651060732</v>
+        <v>-0.2855976176573805</v>
       </c>
       <c r="O3" s="5">
         <v>341</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2248679064568086</v>
+        <v>0.2216019131508812</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2124036193552077</v>
+        <v>0.2092429149463561</v>
       </c>
       <c r="R3" s="5">
         <v>340</v>
@@ -4294,16 +4294,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.221291629975281</v>
+        <v>-0.2394444775036657</v>
       </c>
       <c r="O4" s="5">
         <v>362</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2215167140400358</v>
+        <v>0.220557760286504</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2158883845889257</v>
+        <v>0.2149716296924873</v>
       </c>
       <c r="R4" s="5">
         <v>362</v>
@@ -4479,13 +4479,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>78.77551020408163</v>
+        <v>78.63945578231292</v>
       </c>
       <c r="C3" s="3">
         <v>13.06122448979592</v>
       </c>
       <c r="D3" s="3">
-        <v>8.163265306122449</v>
+        <v>8.299319727891156</v>
       </c>
       <c r="E3" s="3">
         <v>0.9523809523809524</v>
@@ -4494,16 +4494,16 @@
         <v>7.210884353741497</v>
       </c>
       <c r="G3" s="3">
-        <v>0</v>
+        <v>0.1360544217687075</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2686848266364926</v>
+        <v>0.2663118910051152</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2326727226172738</v>
+        <v>0.2285037504602677</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2639634392419071</v>
+        <v>0.2676095822537431</v>
       </c>
       <c r="K3" s="4">
         <v>85.78726456569022</v>
@@ -4547,13 +4547,13 @@
         <v>0.4081632653061225</v>
       </c>
       <c r="H4" s="4">
-        <v>0.320729233539302</v>
+        <v>0.316601453280452</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2438151552655745</v>
+        <v>0.2424479373724963</v>
       </c>
       <c r="J4" s="4">
-        <v>0.255560286267519</v>
+        <v>0.2570212880261702</v>
       </c>
       <c r="K4" s="4">
         <v>87.04229719098485</v>
@@ -4597,13 +4597,13 @@
         <v>0.2721088435374149</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2645757626485283</v>
+        <v>0.2613789591859976</v>
       </c>
       <c r="I5" s="4">
-        <v>0.249265271781267</v>
+        <v>0.2476290272171199</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2405579543176286</v>
+        <v>0.2394097860532309</v>
       </c>
       <c r="K5" s="4">
         <v>87.47156277476991</v>
@@ -4647,13 +4647,13 @@
         <v>0.2721088435374149</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2660674284381063</v>
+        <v>0.2640895735374731</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2179059389279547</v>
+        <v>0.2170659441097127</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2248064485727185</v>
+        <v>0.2271017842057375</v>
       </c>
       <c r="K6" s="4">
         <v>87.04609190615018</v>
@@ -4697,13 +4697,13 @@
         <v>0.1360544217687075</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2383869076608513</v>
+        <v>0.2360249570126236</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2234749080942682</v>
+        <v>0.2220867550615851</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2097857673057082</v>
+        <v>0.2107687556074021</v>
       </c>
       <c r="K7" s="4">
         <v>89.5935027072054</v>
@@ -4747,13 +4747,13 @@
         <v>0.2721088435374149</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2792842411970235</v>
+        <v>0.2745750035797119</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2489196097886648</v>
+        <v>0.2441905972475405</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2551521270434528</v>
+        <v>0.2623770268029356</v>
       </c>
       <c r="K8" s="4">
         <v>84.66564857235382</v>
@@ -4797,13 +4797,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.2702995477641304</v>
+        <v>0.2695957464525537</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2596382527526021</v>
+        <v>0.2593928732764536</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2438293548410006</v>
+        <v>0.2435999315483322</v>
       </c>
       <c r="K9" s="4">
         <v>83.16081262436943</v>
@@ -4847,13 +4847,13 @@
         <v>0.2721088435374149</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2542027373082318</v>
+        <v>0.2509577552150254</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2295997177518343</v>
+        <v>0.226913174689336</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2177801792272032</v>
+        <v>0.2196441928190797</v>
       </c>
       <c r="K10" s="4">
         <v>90.60317460317447</v>
@@ -4897,13 +4897,13 @@
         <v>0.1360544217687075</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2366913548203569</v>
+        <v>0.2354178453699808</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2304188769847412</v>
+        <v>0.2292861650631217</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2197788111256071</v>
+        <v>0.2217845801220716</v>
       </c>
       <c r="K11" s="4">
         <v>88.22393447174807</v>
@@ -4929,13 +4929,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>95.64625850340136</v>
+        <v>95.51020408163265</v>
       </c>
       <c r="C12" s="3">
         <v>2.72108843537415</v>
       </c>
       <c r="D12" s="3">
-        <v>1.63265306122449</v>
+        <v>1.768707482993197</v>
       </c>
       <c r="E12" s="3">
         <v>0.4081632653061225</v>
@@ -4944,16 +4944,16 @@
         <v>1.08843537414966</v>
       </c>
       <c r="G12" s="3">
-        <v>0.1360544217687075</v>
+        <v>0.2721088435374149</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2352664345478903</v>
+        <v>0.2337523111917196</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2248481861426014</v>
+        <v>0.2208935142896441</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2115410133671945</v>
+        <v>0.2122853866323749</v>
       </c>
       <c r="K12" s="4">
         <v>92.17043824332447</v>
@@ -4997,13 +4997,13 @@
         <v>0.1360544217687075</v>
       </c>
       <c r="H13" s="4">
-        <v>0.2936530494579498</v>
+        <v>0.2900764823836902</v>
       </c>
       <c r="I13" s="4">
-        <v>0.225330668017691</v>
+        <v>0.2241237274692943</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2393055629591692</v>
+        <v>0.2460516376549661</v>
       </c>
       <c r="K13" s="4">
         <v>81.93419408579759</v>
@@ -5047,13 +5047,13 @@
         <v>0.1360544217687075</v>
       </c>
       <c r="H14" s="4">
-        <v>0.4285023413011739</v>
+        <v>0.4270042812987774</v>
       </c>
       <c r="I14" s="4">
-        <v>0.3737714861182145</v>
+        <v>0.3701658483481756</v>
       </c>
       <c r="J14" s="4">
-        <v>0.5695820146202505</v>
+        <v>0.5552216349306134</v>
       </c>
       <c r="K14" s="4">
         <v>60.02452681752987</v>
@@ -5079,13 +5079,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>97.55102040816327</v>
+        <v>97.41496598639455</v>
       </c>
       <c r="C15" s="3">
         <v>1.904761904761905</v>
       </c>
       <c r="D15" s="3">
-        <v>0.5442176870748299</v>
+        <v>0.6802721088435374</v>
       </c>
       <c r="E15" s="3">
         <v>0.1360544217687075</v>
@@ -5094,16 +5094,16 @@
         <v>0.2721088435374149</v>
       </c>
       <c r="G15" s="3">
-        <v>0.1360544217687075</v>
+        <v>0.2721088435374149</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2377552337852874</v>
+        <v>0.2354434900480848</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2301472891054214</v>
+        <v>0.2256213782980962</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2137792852870748</v>
+        <v>0.2127555048752218</v>
       </c>
       <c r="K15" s="4">
         <v>93.93877551020434</v>
@@ -5147,13 +5147,13 @@
         <v>0.1360544217687075</v>
       </c>
       <c r="H16" s="4">
-        <v>0.4001035917195703</v>
+        <v>0.4016783208575878</v>
       </c>
       <c r="I16" s="4">
-        <v>0.3052166618539555</v>
+        <v>0.3034057226383133</v>
       </c>
       <c r="J16" s="4">
-        <v>0.566634879539166</v>
+        <v>0.5591229226605497</v>
       </c>
       <c r="K16" s="4">
         <v>60.02952473506402</v>
@@ -5197,13 +5197,13 @@
         <v>0.1360544217687075</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2273496341081062</v>
+        <v>0.2252515311466061</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2144495177096411</v>
+        <v>0.2124544754805343</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2080672361182632</v>
+        <v>0.2093687824918446</v>
       </c>
       <c r="K17" s="4">
         <v>92.86727752325409</v>
@@ -6086,13 +6086,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C3" s="5">
         <v>96</v>
       </c>
       <c r="D3" s="5">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" s="5">
         <v>7</v>
@@ -6101,7 +6101,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="5">
         <v>7</v>
@@ -6482,13 +6482,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C12" s="5">
         <v>20</v>
       </c>
       <c r="D12" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="5">
         <v>3</v>
@@ -6497,7 +6497,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5">
         <v>3</v>
@@ -6614,13 +6614,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="5">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C15" s="5">
         <v>14</v>
       </c>
       <c r="D15" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -6629,7 +6629,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="5">
         <v>1</v>
@@ -6900,22 +6900,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05210567036339144</v>
+        <v>-0.07788234430236685</v>
       </c>
       <c r="O3" s="5">
         <v>320</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2588356415117281</v>
+        <v>0.2557319238497957</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2422545293767273</v>
+        <v>0.2351484377292929</v>
       </c>
       <c r="R3" s="5">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1673042143200807</v>
+        <v>0.1489192190124413</v>
       </c>
       <c r="O4" s="5">
         <v>257</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2729317752177752</v>
+        <v>0.2712571156493997</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2146751242765272</v>
+        <v>0.2141566773331092</v>
       </c>
       <c r="R4" s="5">
         <v>257</v>
@@ -7198,16 +7198,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1161720967145131</v>
+        <v>0.09443836715331599</v>
       </c>
       <c r="O3" s="5">
         <v>361</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2587521640772868</v>
+        <v>0.2577255638972646</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2519203203302235</v>
+        <v>0.2509398332853711</v>
       </c>
       <c r="R3" s="5">
         <v>360</v>
@@ -7257,16 +7257,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4428475574635733</v>
+        <v>0.4161695653088202</v>
       </c>
       <c r="O4" s="5">
         <v>255</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3598072784024535</v>
+        <v>0.3525217731297229</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2313680700883081</v>
+        <v>0.2294495175942327</v>
       </c>
       <c r="R4" s="5">
         <v>255</v>
@@ -7496,16 +7496,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02677545433932009</v>
+        <v>-0.06719979698416978</v>
       </c>
       <c r="O3" s="5">
         <v>319</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2616401339763661</v>
+        <v>0.2564550107389972</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2426203566410948</v>
+        <v>0.2400111300743705</v>
       </c>
       <c r="R3" s="5">
         <v>318</v>
@@ -7555,16 +7555,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06156456835721322</v>
+        <v>0.04075809453144075</v>
       </c>
       <c r="O4" s="5">
         <v>352</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2623502581986522</v>
+        <v>0.2610979826827058</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2562361345936407</v>
+        <v>0.2554695939717985</v>
       </c>
       <c r="R4" s="5">
         <v>352</v>
@@ -7794,16 +7794,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06140516992203723</v>
+        <v>-0.09091256000851899</v>
       </c>
       <c r="O3" s="5">
         <v>322</v>
       </c>
       <c r="P3" s="4">
-        <v>0.242864670178938</v>
+        <v>0.239287776263432</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2198412721208129</v>
+        <v>0.2181998739709277</v>
       </c>
       <c r="R3" s="5">
         <v>321</v>
@@ -7853,16 +7853,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1101429476718305</v>
+        <v>0.1058505486010688</v>
       </c>
       <c r="O4" s="5">
         <v>312</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2856580233802246</v>
+        <v>0.2852521135917159</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2170246003519183</v>
+        <v>0.2170037416869486</v>
       </c>
       <c r="R4" s="5">
         <v>312</v>
@@ -8092,16 +8092,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0921354781380585</v>
+        <v>-0.1229020134704371</v>
       </c>
       <c r="O3" s="5">
         <v>328</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2236029128414728</v>
+        <v>0.2219674085329618</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2183766830978613</v>
+        <v>0.2175884904638663</v>
       </c>
       <c r="R3" s="5">
         <v>328</v>
@@ -8151,16 +8151,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03286159159880963</v>
+        <v>-0.07031936797119442</v>
       </c>
       <c r="O4" s="5">
         <v>353</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2450928225115931</v>
+        <v>0.2419720700353168</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2290472718525063</v>
+        <v>0.2270937836446529</v>
       </c>
       <c r="R4" s="5">
         <v>353</v>
